--- a/erp-server/erp-server-srm/src/main/resources/excel/salesSharingExport.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/salesSharingExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -74,7 +74,7 @@
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.skuName}</t>
+    <t>{.productName}</t>
   </si>
   <si>
     <t>{.saleStateName}</t>
